--- a/e2e_automation/data/test_data.xlsx
+++ b/e2e_automation/data/test_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\whddl\OneDrive\바탕 화면\cl\e2e_automation\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Osstem\Desktop\cl\clse\e2e_automation\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B7C86FC-734F-43D2-854B-697360B25BE6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F515312-EE25-4ABC-8DE9-C4B4D7AE6BBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12060" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="39960" yWindow="1560" windowWidth="28800" windowHeight="15885" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="test_suite (2)" sheetId="6" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="122">
   <si>
     <t>test_id</t>
   </si>
@@ -222,6 +222,9 @@
     <t>wait_after</t>
   </si>
   <si>
+    <t>skip_navigate</t>
+  </si>
+  <si>
     <t>TC_SUITE_001</t>
   </si>
   <si>
@@ -249,6 +252,9 @@
     <t>h1 텍스트 일치 확인</t>
   </si>
   <si>
+    <t>Example Domain</t>
+  </si>
+  <si>
     <t>TC_SUITE_004</t>
   </si>
   <si>
@@ -306,6 +312,9 @@
     <t>tab-menu</t>
   </si>
   <si>
+    <t>.tab-content</t>
+  </si>
+  <si>
     <t>text</t>
   </si>
   <si>
@@ -336,18 +345,40 @@
     <t>옵션1</t>
   </si>
   <si>
-    <t>logo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[부산] [치과위생사] 치과위생사선생님을 모십니다.</t>
-  </si>
-  <si>
-    <t>Example Domain</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>.tab-content</t>
+    <t>TC_SUITE_010</t>
+  </si>
+  <si>
+    <t>로그인 페이지 접속</t>
+  </si>
+  <si>
+    <t>TC_SUITE_011</t>
+  </si>
+  <si>
+    <t>input</t>
+  </si>
+  <si>
+    <t>아이디 입력</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>TC_SUITE_012</t>
+  </si>
+  <si>
+    <t>패스워드 입력</t>
+  </si>
+  <si>
+    <t>TC_SUITE_013</t>
+  </si>
+  <si>
+    <t>로그인 버튼 클릭</t>
+  </si>
+  <si>
+    <t>login-btn</t>
+  </si>
+  <si>
+    <t>.input</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -355,11 +386,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>h2.subtitle</t>
+    <t xml:space="preserve">.btn </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>verify_locator_value</t>
+    <t>mpms1234!@</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">testdoc01@dev00003 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -383,10 +418,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF1A1A1A"/>
-      <name val="Courier New"/>
-      <family val="3"/>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -406,15 +443,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -713,613 +752,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37AF8345-CCB9-4885-8159-E5CE564A5070}">
-  <dimension ref="A1:W10"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G1" t="s">
-        <v>56</v>
-      </c>
-      <c r="H1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I1" t="s">
-        <v>58</v>
-      </c>
-      <c r="J1" t="s">
-        <v>59</v>
-      </c>
-      <c r="K1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L1" t="s">
-        <v>23</v>
-      </c>
-      <c r="M1" t="s">
-        <v>24</v>
-      </c>
-      <c r="N1" t="s">
-        <v>25</v>
-      </c>
-      <c r="O1" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R1" t="s">
-        <v>60</v>
-      </c>
-      <c r="S1" t="s">
-        <v>11</v>
-      </c>
-      <c r="T1" t="s">
-        <v>61</v>
-      </c>
-      <c r="U1" t="s">
-        <v>62</v>
-      </c>
-      <c r="V1" t="s">
-        <v>63</v>
-      </c>
-      <c r="W1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>66</v>
-      </c>
-      <c r="B3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>71</v>
-      </c>
-      <c r="B4" t="s">
-        <v>72</v>
-      </c>
-      <c r="C4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E4" t="s">
-        <v>70</v>
-      </c>
-      <c r="R4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>74</v>
-      </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" t="s">
-        <v>75</v>
-      </c>
-      <c r="D5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" t="s">
-        <v>15</v>
-      </c>
-      <c r="S5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>76</v>
-      </c>
-      <c r="B6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C6" t="s">
-        <v>78</v>
-      </c>
-      <c r="D6" t="s">
-        <v>79</v>
-      </c>
-      <c r="E6" t="s">
-        <v>80</v>
-      </c>
-      <c r="G6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H6" t="s">
-        <v>81</v>
-      </c>
-      <c r="J6" t="s">
-        <v>82</v>
-      </c>
-      <c r="V6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>84</v>
-      </c>
-      <c r="B7" t="s">
-        <v>77</v>
-      </c>
-      <c r="C7" t="s">
-        <v>85</v>
-      </c>
-      <c r="D7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" t="s">
-        <v>86</v>
-      </c>
-      <c r="F7" t="s">
-        <v>87</v>
-      </c>
-      <c r="G7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H7" t="s">
-        <v>88</v>
-      </c>
-      <c r="I7" t="s">
-        <v>87</v>
-      </c>
-      <c r="J7" t="s">
-        <v>89</v>
-      </c>
-      <c r="V7" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>90</v>
-      </c>
-      <c r="B8" t="s">
-        <v>77</v>
-      </c>
-      <c r="C8" t="s">
-        <v>91</v>
-      </c>
-      <c r="D8" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" t="s">
-        <v>92</v>
-      </c>
-      <c r="F8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G8" t="s">
-        <v>33</v>
-      </c>
-      <c r="H8" t="s">
-        <v>106</v>
-      </c>
-      <c r="J8" t="s">
-        <v>93</v>
-      </c>
-      <c r="R8" t="s">
-        <v>94</v>
-      </c>
-      <c r="V8" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>96</v>
-      </c>
-      <c r="B9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" t="s">
-        <v>97</v>
-      </c>
-      <c r="K9" t="s">
-        <v>35</v>
-      </c>
-      <c r="L9" t="s">
-        <v>33</v>
-      </c>
-      <c r="M9" t="s">
-        <v>34</v>
-      </c>
-      <c r="O9" t="s">
-        <v>33</v>
-      </c>
-      <c r="P9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>98</v>
-      </c>
-      <c r="B10" t="s">
-        <v>99</v>
-      </c>
-      <c r="C10" t="s">
-        <v>100</v>
-      </c>
-      <c r="D10" t="s">
-        <v>79</v>
-      </c>
-      <c r="E10" t="s">
-        <v>101</v>
-      </c>
-      <c r="T10" t="s">
-        <v>93</v>
-      </c>
-      <c r="U10" t="s">
-        <v>102</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:L3"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K1" t="s">
-        <v>11</v>
-      </c>
-      <c r="L1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H2" t="s">
-        <v>36</v>
-      </c>
-      <c r="J2" t="s">
-        <v>37</v>
-      </c>
-      <c r="L2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" t="s">
-        <v>40</v>
-      </c>
-      <c r="E3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" t="s">
-        <v>41</v>
-      </c>
-      <c r="G3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" t="s">
-        <v>42</v>
-      </c>
-      <c r="I3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J3" t="s">
-        <v>37</v>
-      </c>
-      <c r="L3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:W3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C440CF55-3EC6-4E1B-B84D-0E728D70404A}">
+  <dimension ref="A1:X14"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.5" bestFit="1" customWidth="1"/>
@@ -1344,9 +778,10 @@
     <col min="21" max="21" width="11.625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="11.375" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1369,7 +804,7 @@
         <v>56</v>
       </c>
       <c r="H1" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="I1" t="s">
         <v>58</v>
@@ -1416,10 +851,13 @@
       <c r="W1" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
@@ -1428,44 +866,800 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E4" t="s">
+        <v>71</v>
+      </c>
+      <c r="R4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>76</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
         <v>77</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" t="s">
+        <v>15</v>
+      </c>
+      <c r="S5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>78</v>
       </c>
-      <c r="D3" t="s">
+      <c r="B6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G6" t="s">
         <v>19</v>
       </c>
-      <c r="E3" t="s">
+      <c r="H6" t="s">
+        <v>83</v>
+      </c>
+      <c r="J6" t="s">
+        <v>84</v>
+      </c>
+      <c r="V6" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>86</v>
+      </c>
+      <c r="B7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C7" t="s">
+        <v>87</v>
+      </c>
+      <c r="D7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" t="s">
+        <v>88</v>
+      </c>
+      <c r="F7" t="s">
+        <v>89</v>
+      </c>
+      <c r="G7" t="s">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s">
+        <v>90</v>
+      </c>
+      <c r="I7" t="s">
+        <v>89</v>
+      </c>
+      <c r="J7" t="s">
+        <v>91</v>
+      </c>
+      <c r="V7" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>92</v>
+      </c>
+      <c r="B8" t="s">
+        <v>79</v>
+      </c>
+      <c r="C8" t="s">
+        <v>93</v>
+      </c>
+      <c r="D8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" t="s">
+        <v>94</v>
+      </c>
+      <c r="F8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G8" t="s">
+        <v>33</v>
+      </c>
+      <c r="H8" t="s">
+        <v>95</v>
+      </c>
+      <c r="J8" t="s">
+        <v>96</v>
+      </c>
+      <c r="R8" t="s">
+        <v>97</v>
+      </c>
+      <c r="V8" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>99</v>
+      </c>
+      <c r="B9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" t="s">
+        <v>100</v>
+      </c>
+      <c r="K9" t="s">
+        <v>35</v>
+      </c>
+      <c r="L9" t="s">
+        <v>33</v>
+      </c>
+      <c r="M9" t="s">
+        <v>34</v>
+      </c>
+      <c r="O9" t="s">
+        <v>33</v>
+      </c>
+      <c r="P9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>101</v>
+      </c>
+      <c r="B10" t="s">
+        <v>102</v>
+      </c>
+      <c r="C10" t="s">
         <v>103</v>
       </c>
-      <c r="F3">
-        <v>17</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="D10" t="s">
+        <v>81</v>
+      </c>
+      <c r="E10" t="s">
+        <v>104</v>
+      </c>
+      <c r="T10" t="s">
+        <v>96</v>
+      </c>
+      <c r="U10" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>106</v>
+      </c>
+      <c r="B11" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" t="s">
         <v>107</v>
       </c>
-      <c r="H3" t="s">
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>108</v>
       </c>
-      <c r="J3" t="s">
-        <v>93</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="V3">
-        <v>2</v>
+      <c r="B12" t="s">
+        <v>109</v>
+      </c>
+      <c r="C12" t="s">
+        <v>110</v>
+      </c>
+      <c r="D12" t="s">
+        <v>81</v>
+      </c>
+      <c r="E12" t="s">
+        <v>44</v>
+      </c>
+      <c r="K12" t="s">
+        <v>47</v>
+      </c>
+      <c r="X12" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>112</v>
+      </c>
+      <c r="B13" t="s">
+        <v>109</v>
+      </c>
+      <c r="C13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D13" t="s">
+        <v>81</v>
+      </c>
+      <c r="E13" t="s">
+        <v>45</v>
+      </c>
+      <c r="K13" t="s">
+        <v>48</v>
+      </c>
+      <c r="X13" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>114</v>
+      </c>
+      <c r="B14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" t="s">
+        <v>115</v>
+      </c>
+      <c r="D14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E14" t="s">
+        <v>116</v>
+      </c>
+      <c r="X14" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:L3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:X5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.75" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.75" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.75" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.75" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="21.125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="21.125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>56</v>
+      </c>
+      <c r="H1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I1" t="s">
+        <v>58</v>
+      </c>
+      <c r="J1" t="s">
+        <v>59</v>
+      </c>
+      <c r="K1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M1" t="s">
+        <v>24</v>
+      </c>
+      <c r="N1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>29</v>
+      </c>
+      <c r="R1" t="s">
+        <v>60</v>
+      </c>
+      <c r="S1" t="s">
+        <v>11</v>
+      </c>
+      <c r="T1" t="s">
+        <v>61</v>
+      </c>
+      <c r="U1" t="s">
+        <v>62</v>
+      </c>
+      <c r="V1" t="s">
+        <v>63</v>
+      </c>
+      <c r="W1" t="s">
+        <v>64</v>
+      </c>
+      <c r="X1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" t="s">
+        <v>117</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="X3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C4" t="s">
+        <v>113</v>
+      </c>
+      <c r="D4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" t="s">
+        <v>117</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="X4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
+        <v>115</v>
+      </c>
+      <c r="D5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E5" t="s">
+        <v>119</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="W5">
+        <v>30</v>
+      </c>
+      <c r="X5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="K4" r:id="rId1" xr:uid="{1065E191-75D8-4388-8B79-5B906BEEDDE5}"/>
+    <hyperlink ref="K3" r:id="rId2" xr:uid="{8FD97A4C-BE17-451C-BCA8-E95D2F51F4C5}"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/e2e_automation/data/test_data.xlsx
+++ b/e2e_automation/data/test_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Osstem\Desktop\cl\clse\e2e_automation\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F515312-EE25-4ABC-8DE9-C4B4D7AE6BBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4B5E8C9-B816-4C47-9BF3-10B86D26F860}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="39960" yWindow="1560" windowWidth="28800" windowHeight="15885" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1648,7 +1648,7 @@
         <v>2</v>
       </c>
       <c r="W5">
-        <v>30</v>
+        <v>3000</v>
       </c>
       <c r="X5" t="s">
         <v>111</v>
